--- a/LastFPS/Excel/Battle.xlsx
+++ b/LastFPS/Excel/Battle.xlsx
@@ -631,10 +631,9 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=6))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=8))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=10))))</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=6))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=8))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=10))))</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>100.000000</t>
@@ -664,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=10))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=7),(EnemyDefinition="/Game/Data/Enemy/Shooter/DA_Char_ShooterEnemy.DA_Char_ShooterEnemy",Count=3))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Enemy/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=5),(EnemyDefinition="/Game/Data/Enemy/Shooter/DA_Char_ShooterEnemy.DA_Char_ShooterEnemy",Count=5))))</t>
+          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=10))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=7),(EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Shooter/DA_Char_ShooterEnemy.DA_Char_ShooterEnemy",Count=3))),(DelayBeforeWave=2.000000,SpawnInterval=0.350000,SpawnBatchSize=3,bShuffleSpawnPoints=True,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Attacker/DA_Char_AttackerEnemy.DA_Char_AttackerEnemy",Count=5),(EnemyDefinition="/Game/Data/Primary/Characters/Enemies/Shooter/DA_Char_ShooterEnemy.DA_Char_ShooterEnemy",Count=5))))</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -701,10 +700,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.000000,SpawnBatchSize=1,bShuffleSpawnPoints=False,Units=((EnemyDefinition="/Game/Data/Enemy/ToiletBoss/DA_Char_ToiletBoss.DA_Char_ToiletBoss",Count=1))))</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>((DelayBeforeWave=0.000000,SpawnInterval=0.000000,SpawnBatchSize=1,bShuffleSpawnPoints=False,Units=((EnemyDefinition="/Game/Data/Primary/Characters/Enemies/ToiletBoss/DA_Char_ToiletBoss.DA_Char_ToiletBoss",Count=1))))</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>100.000000</t>
